--- a/docs/parameter-hallucination/shortcut-gap-reanalysis/aitable/aitable_cli_param_hallucination_analysis.xlsx
+++ b/docs/parameter-hallucination/shortcut-gap-reanalysis/aitable/aitable_cli_param_hallucination_analysis.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇报总览" sheetId="1" r:id="R2e7e8df0c3114cc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数问题明细" sheetId="2" r:id="Rc746bd9a86384b30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兜底解决方案" sheetId="3" r:id="R47b7ef95748d492c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前无法解决" sheetId="4" r:id="Re781e23d75f642b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析依据" sheetId="5" r:id="R3e21333374864d68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇报总览" sheetId="1" r:id="Rda32f7a387e24282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数问题明细" sheetId="2" r:id="R9b2bb0a852a14912"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兜底解决方案" sheetId="3" r:id="R1aae149ee26a49e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前无法解决" sheetId="4" r:id="Rb2cca87b40044be4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析依据" sheetId="5" r:id="R6e4aaf7e36d546e8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -532,7 +532,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>冻结基线 5f906bf8b61bc54a75f6c2b46219a1deb682b600｜正式别名表未修改｜候选、报告、五页工作簿独立交付</x:v>
+        <x:v>冻结基线 f4474b57eb1db23b1638b9574be2f5dca368a360｜正式别名表未修改｜候选、报告、五页工作簿独立交付</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -762,7 +762,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>冻结基线 5f906bf8b61bc54a75f6c2b46219a1deb682b600｜逐命令核对真实 Help/Cobra、运行时 Schema、Skill 与正式别名表</x:v>
+        <x:v>冻结基线 f4474b57eb1db23b1638b9574be2f5dca368a360｜逐命令核对真实 Help/Cobra、运行时 Schema、Skill 与正式别名表</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -900,7 +900,7 @@
         <x:v>sourceConfig、自动同步配置、字段 ID 列表三种结构并存</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>复用/新增跨命令 concept；generic config/json 和单字段 ID 阻断</x:v>
+        <x:v>仅明确 sourceConfig 拼写进入 concept；宽泛 datasource-config 保持歧义，generic config/json 和单字段 ID 阻断</x:v>
       </x:c>
       <x:c r="F9" s="18" t="str">
         <x:v>部分兜底</x:v>
@@ -923,7 +923,7 @@
         <x:v>两个 ID + 两类 JSON + 字段列表角色冲突</x:v>
       </x:c>
       <x:c r="E10" s="19" t="str">
-        <x:v>按实体 concept 绑定；generic id/config 保护</x:v>
+        <x:v>按实体 concept 绑定；宽泛 datasource-config 无法选择 JSON 角色，保持歧义</x:v>
       </x:c>
       <x:c r="F10" s="19" t="str">
         <x:v>部分兜底</x:v>
@@ -1038,7 +1038,7 @@
         <x:v>field-ids 是输出，不是请求字段；config 角色不完整</x:v>
       </x:c>
       <x:c r="E15" s="18" t="str">
-        <x:v>绑定 sourceConfig；field-ids 阻断；generic config 歧义</x:v>
+        <x:v>仅明确 sourceConfig 拼写可绑定；field-ids 阻断，宽泛 datasource-config 保持歧义</x:v>
       </x:c>
       <x:c r="F15" s="18" t="str">
         <x:v>部分兜底</x:v>
@@ -1211,10 +1211,10 @@
 aitable +datasource-get-fields</x:v>
       </x:c>
       <x:c r="E8" s="19" t="str">
-        <x:v>source-config, datasource-config, data-source-config, source-config-json → source-config</x:v>
+        <x:v>source-config, source-config-json → source-config</x:v>
       </x:c>
       <x:c r="F8" s="19" t="str">
-        <x:v>config, source, payload, data, json, fields, auto-sync-setting</x:v>
+        <x:v>config, source, payload, data, json, fields, auto-sync-setting, datasource-config, data-source-config</x:v>
       </x:c>
       <x:c r="G8" s="19" t="str">
         <x:v>中风险</x:v>
@@ -1320,7 +1320,7 @@
         <x:v>aitable +datasource-create</x:v>
       </x:c>
       <x:c r="C13" s="18" t="str">
-        <x:v>bind 3 / alias 4 / block 7 / ambiguous 2</x:v>
+        <x:v>bind 3 / alias 4 / block 7 / ambiguous 4</x:v>
       </x:c>
       <x:c r="D13" s="18" t="str">
         <x:v>aitable +datasource-create</x:v>
@@ -1329,7 +1329,7 @@
         <x:v>仅在本命令启用已验证的 bind / scoped alias；其余近似参数保持拦截或歧义保护</x:v>
       </x:c>
       <x:c r="F13" s="18" t="str">
-        <x:v>table-id, field-id, config, source, payload, data, json, id, type</x:v>
+        <x:v>table-id, field-id, config, source, payload, data, json, id, type, datasource-config, data-source-config</x:v>
       </x:c>
       <x:c r="G13" s="18" t="str">
         <x:v>严格命令域</x:v>
@@ -1343,7 +1343,7 @@
         <x:v>aitable +datasource-update</x:v>
       </x:c>
       <x:c r="C14" s="19" t="str">
-        <x:v>bind 4 / alias 3 / block 9 / ambiguous 2</x:v>
+        <x:v>bind 4 / alias 3 / block 9 / ambiguous 4</x:v>
       </x:c>
       <x:c r="D14" s="19" t="str">
         <x:v>aitable +datasource-update</x:v>
@@ -1352,7 +1352,7 @@
         <x:v>仅在本命令启用已验证的 bind / scoped alias；其余近似参数保持拦截或歧义保护</x:v>
       </x:c>
       <x:c r="F14" s="19" t="str">
-        <x:v>datasource-type, data-source-type, source-type, field-id, config, source, payload, data, json, id, type</x:v>
+        <x:v>datasource-type, data-source-type, source-type, field-id, config, source, payload, data, json, id, type, datasource-config, data-source-config</x:v>
       </x:c>
       <x:c r="G14" s="19" t="str">
         <x:v>严格命令域</x:v>
@@ -1458,7 +1458,7 @@
         <x:v>aitable +datasource-get-fields</x:v>
       </x:c>
       <x:c r="C19" s="18" t="str">
-        <x:v>bind 2 / alias 1 / block 3 / ambiguous 4</x:v>
+        <x:v>bind 2 / alias 1 / block 3 / ambiguous 6</x:v>
       </x:c>
       <x:c r="D19" s="18" t="str">
         <x:v>aitable +datasource-get-fields</x:v>
@@ -1467,7 +1467,7 @@
         <x:v>仅在本命令启用已验证的 bind / scoped alias；其余近似参数保持拦截或歧义保护</x:v>
       </x:c>
       <x:c r="F19" s="18" t="str">
-        <x:v>table-id, field-id, field-ids, id, type, source, config</x:v>
+        <x:v>table-id, field-id, field-ids, id, type, source, config, datasource-config, data-source-config</x:v>
       </x:c>
       <x:c r="G19" s="18" t="str">
         <x:v>严格命令域</x:v>
@@ -1628,7 +1628,7 @@
         <x:v>部分兜底</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>复用/新增跨命令 concept；generic config/json 和单字段 ID 阻断</x:v>
+        <x:v>仅明确 sourceConfig 拼写进入 concept；宽泛 datasource-config 保持歧义，generic config/json 和单字段 ID 阻断</x:v>
       </x:c>
       <x:c r="F9" s="18" t="str">
         <x:v>需修改真实 CLI/框架，或由 Agent 明确选择真实参数；别名表不做查找、转换、枚举翻译或基数变化</x:v>
@@ -1648,7 +1648,7 @@
         <x:v>部分兜底</x:v>
       </x:c>
       <x:c r="E10" s="19" t="str">
-        <x:v>按实体 concept 绑定；generic id/config 保护</x:v>
+        <x:v>按实体 concept 绑定；宽泛 datasource-config 无法选择 JSON 角色，保持歧义</x:v>
       </x:c>
       <x:c r="F10" s="19" t="str">
         <x:v>需修改真实 CLI/框架，或由 Agent 明确选择真实参数；别名表不做查找、转换、枚举翻译或基数变化</x:v>
@@ -1748,7 +1748,7 @@
         <x:v>部分兜底</x:v>
       </x:c>
       <x:c r="E15" s="18" t="str">
-        <x:v>绑定 sourceConfig；field-ids 阻断；generic config 歧义</x:v>
+        <x:v>仅明确 sourceConfig 拼写可绑定；field-ids 阻断，宽泛 datasource-config 保持歧义</x:v>
       </x:c>
       <x:c r="F15" s="18" t="str">
         <x:v>需修改真实 CLI/框架，或由 Agent 明确选择真实参数；别名表不做查找、转换、枚举翻译或基数变化</x:v>
@@ -1808,7 +1808,7 @@
         <x:v>冻结基线</x:v>
       </x:c>
       <x:c r="B5" s="18" t="str">
-        <x:v>origin/main@5f906bf8b61bc54a75f6c2b46219a1deb682b600</x:v>
+        <x:v>origin/main@f4474b57eb1db23b1638b9574be2f5dca368a360</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
         <x:v>通过</x:v>
